--- a/Eastern Regions Report 3.xlsx
+++ b/Eastern Regions Report 3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Cindy\Desktop\Chris - Videos\Excel 2019\Module 8 - Formulas and Functions\Module 8 Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Excel Beginner\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A04CDDB6-6767-4AC6-8AEC-CD01BFE74929}" xr6:coauthVersionLast="41" xr6:coauthVersionMax="41" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85D0ACBA-C594-4D48-B285-48190611D99E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -569,6 +569,14 @@
       <c r="F6">
         <v>135</v>
       </c>
+      <c r="G6">
+        <f>SUM(C6:F6)</f>
+        <v>560</v>
+      </c>
+      <c r="H6">
+        <f>G6*$H$2</f>
+        <v>84</v>
+      </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B7" t="s">
@@ -586,6 +594,14 @@
       <c r="F7">
         <v>165</v>
       </c>
+      <c r="G7">
+        <f t="shared" ref="G7:G10" si="0">SUM(C7:F7)</f>
+        <v>740</v>
+      </c>
+      <c r="H7">
+        <f t="shared" ref="H7:H10" si="1">G7*$H$2</f>
+        <v>111</v>
+      </c>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B8" t="s">
@@ -603,6 +619,14 @@
       <c r="F8">
         <v>205</v>
       </c>
+      <c r="G8">
+        <f t="shared" si="0"/>
+        <v>855</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="1"/>
+        <v>128.25</v>
+      </c>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
@@ -620,6 +644,14 @@
       <c r="F9">
         <v>225</v>
       </c>
+      <c r="G9">
+        <f t="shared" si="0"/>
+        <v>760</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="1"/>
+        <v>114</v>
+      </c>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
@@ -637,21 +669,101 @@
       <c r="F10">
         <v>250</v>
       </c>
+      <c r="G10">
+        <f t="shared" si="0"/>
+        <v>850</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="1"/>
+        <v>127.5</v>
+      </c>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
         <v>4</v>
       </c>
+      <c r="C12">
+        <f>SUM(C6:C10)</f>
+        <v>890</v>
+      </c>
+      <c r="D12">
+        <f t="shared" ref="D12:H12" si="2">SUM(D6:D10)</f>
+        <v>930</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="2"/>
+        <v>965</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="2"/>
+        <v>980</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="2"/>
+        <v>3765</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="2"/>
+        <v>564.75</v>
+      </c>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B14" t="s">
         <v>14</v>
       </c>
+      <c r="C14">
+        <f>AVERAGE(C6:C10)</f>
+        <v>178</v>
+      </c>
+      <c r="D14">
+        <f t="shared" ref="D14:H14" si="3">AVERAGE(D6:D10)</f>
+        <v>186</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="3"/>
+        <v>193</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="3"/>
+        <v>196</v>
+      </c>
+      <c r="G14">
+        <f t="shared" si="3"/>
+        <v>753</v>
+      </c>
+      <c r="H14">
+        <f t="shared" si="3"/>
+        <v>112.95</v>
+      </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B16" t="s">
         <v>15</v>
       </c>
+      <c r="C16">
+        <f>MAX(C6:C10)</f>
+        <v>220</v>
+      </c>
+      <c r="D16">
+        <f t="shared" ref="D16:H16" si="4">MAX(D6:D10)</f>
+        <v>210</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="4"/>
+        <v>240</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="4"/>
+        <v>250</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="4"/>
+        <v>855</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="4"/>
+        <v>128.25</v>
+      </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
@@ -699,6 +811,14 @@
       <c r="F22">
         <v>550</v>
       </c>
+      <c r="G22">
+        <f>SUM(C22:F22)</f>
+        <v>1940</v>
+      </c>
+      <c r="H22">
+        <f>G22*$H$2</f>
+        <v>291</v>
+      </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B23" t="s">
@@ -716,6 +836,14 @@
       <c r="F23">
         <v>475</v>
       </c>
+      <c r="G23">
+        <f t="shared" ref="G23:G26" si="5">SUM(C23:F23)</f>
+        <v>1495</v>
+      </c>
+      <c r="H23">
+        <f t="shared" ref="H23:H26" si="6">G23*$H$2</f>
+        <v>224.25</v>
+      </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B24" t="s">
@@ -733,6 +861,14 @@
       <c r="F24">
         <v>350</v>
       </c>
+      <c r="G24">
+        <f t="shared" si="5"/>
+        <v>955</v>
+      </c>
+      <c r="H24">
+        <f t="shared" si="6"/>
+        <v>143.25</v>
+      </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
@@ -750,6 +886,14 @@
       <c r="F25">
         <v>685</v>
       </c>
+      <c r="G25">
+        <f t="shared" si="5"/>
+        <v>2250</v>
+      </c>
+      <c r="H25">
+        <f t="shared" si="6"/>
+        <v>337.5</v>
+      </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
@@ -767,20 +911,100 @@
       <c r="F26">
         <v>610</v>
       </c>
+      <c r="G26">
+        <f t="shared" si="5"/>
+        <v>1895</v>
+      </c>
+      <c r="H26">
+        <f t="shared" si="6"/>
+        <v>284.25</v>
+      </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
         <v>4</v>
       </c>
+      <c r="C28">
+        <f>SUM(C22:C26)</f>
+        <v>1700</v>
+      </c>
+      <c r="D28">
+        <f t="shared" ref="D28:H28" si="7">SUM(D22:D26)</f>
+        <v>1825</v>
+      </c>
+      <c r="E28">
+        <f t="shared" si="7"/>
+        <v>2340</v>
+      </c>
+      <c r="F28">
+        <f t="shared" si="7"/>
+        <v>2670</v>
+      </c>
+      <c r="G28">
+        <f>SUM(G22:G26)</f>
+        <v>8535</v>
+      </c>
+      <c r="H28">
+        <f>SUM(H22:H26)</f>
+        <v>1280.25</v>
+      </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
         <v>14</v>
       </c>
+      <c r="C30">
+        <f>AVERAGE(C22:C26)</f>
+        <v>340</v>
+      </c>
+      <c r="D30">
+        <f t="shared" ref="D30:H30" si="8">AVERAGE(D22:D26)</f>
+        <v>365</v>
+      </c>
+      <c r="E30">
+        <f t="shared" si="8"/>
+        <v>468</v>
+      </c>
+      <c r="F30">
+        <f t="shared" si="8"/>
+        <v>534</v>
+      </c>
+      <c r="G30">
+        <f t="shared" si="8"/>
+        <v>1707</v>
+      </c>
+      <c r="H30">
+        <f t="shared" si="8"/>
+        <v>256.05</v>
+      </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B32" t="s">
         <v>15</v>
+      </c>
+      <c r="C32">
+        <f>MAX(C22:C26)</f>
+        <v>500</v>
+      </c>
+      <c r="D32">
+        <f t="shared" ref="D32:H32" si="9">MAX(D22:D26)</f>
+        <v>525</v>
+      </c>
+      <c r="E32">
+        <f t="shared" si="9"/>
+        <v>755</v>
+      </c>
+      <c r="F32">
+        <f t="shared" si="9"/>
+        <v>685</v>
+      </c>
+      <c r="G32">
+        <f t="shared" si="9"/>
+        <v>2250</v>
+      </c>
+      <c r="H32">
+        <f t="shared" si="9"/>
+        <v>337.5</v>
       </c>
     </row>
   </sheetData>
